--- a/utils/import_data/artworks/伪满皇宫_展品清单.xlsx
+++ b/utils/import_data/artworks/伪满皇宫_展品清单.xlsx
@@ -1099,12 +1099,7 @@
           <t>Watanabe Huashan The Daughter of the Knight</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>作者：渡边华山(1793-1841)，原名渡边定静，字子安，一字伯登，通称登，号华山，多以此号行世。斋号有寓绘堂、全乐堂、金暾居、昨非居士、随安居士。
-此画作属华山青年时期的作品。此画为绢本设色，立轴，无题跋，署穷款：华山戏墨。通纵：125厘米，通横：68厘米；画心纵：40.5厘米，画心横：57厘米。画中所绘一位日本女子，身着和服，头饰素栉，双目凝神，回望飞燕，肌肤似雪，青丝如云，柳叶有情，樱桃微启，表现了江户时代贵族女子雍容华贵、安详恬静、风情万种的优雅神态。此画具有鲜明的日本民族风格和浓郁的人文精神，细微之处又显露出中国传统仕女绘画艺术的痕迹。画中人物仪态端庄，衣裳简劲，色彩柔丽，清雅中不失娇美，淡定中不失活力，在其扶栏顾盼的瞬间，生动唯美，气韵传神，流露出她丰富多情的内心世界和看似柔弱内敛、实则蓬勃坚韧的生命气质。常言道：“容情入境，心如其画”，此画表现了作者深邃细腻、志趣高雅的审美境界和独特精湛的艺术修养。</t>
-        </is>
-      </c>
+      <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
           <t>collection/475 · en/1639</t>
